--- a/final_data_pipeline/output/311615_elec_options.xlsx
+++ b/final_data_pipeline/output/311615_elec_options.xlsx
@@ -924,7 +924,7 @@
         <v>118</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -1013,7 +1013,7 @@
         <v>118</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1102,7 +1102,7 @@
         <v>118</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1191,7 +1191,7 @@
         <v>118</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1280,7 +1280,7 @@
         <v>118</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1369,7 +1369,7 @@
         <v>118</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1458,7 +1458,7 @@
         <v>118</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1547,7 +1547,7 @@
         <v>118</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1636,7 +1636,7 @@
         <v>118</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1725,7 +1725,7 @@
         <v>118</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1814,7 +1814,7 @@
         <v>118</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1903,7 +1903,7 @@
         <v>118</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -1992,7 +1992,7 @@
         <v>118</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2081,7 +2081,7 @@
         <v>118</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2170,7 +2170,7 @@
         <v>118</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2259,7 +2259,7 @@
         <v>118</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2348,7 +2348,7 @@
         <v>118</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2437,7 +2437,7 @@
         <v>118</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2526,7 +2526,7 @@
         <v>118</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2615,7 +2615,7 @@
         <v>118</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2704,7 +2704,7 @@
         <v>118</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2793,7 +2793,7 @@
         <v>118</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2882,7 +2882,7 @@
         <v>118</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -2971,7 +2971,7 @@
         <v>118</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -6531,7 +6531,7 @@
         <v>118</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -6620,7 +6620,7 @@
         <v>118</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -6709,7 +6709,7 @@
         <v>118</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -6798,7 +6798,7 @@
         <v>118</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE68">
         <v>8000</v>
@@ -6887,7 +6887,7 @@
         <v>118</v>
       </c>
       <c r="AD69">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE69">
         <v>8000</v>
@@ -6976,7 +6976,7 @@
         <v>118</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7065,7 +7065,7 @@
         <v>118</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7154,7 +7154,7 @@
         <v>118</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -7243,7 +7243,7 @@
         <v>118</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7332,7 +7332,7 @@
         <v>118</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -7421,7 +7421,7 @@
         <v>118</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -7510,7 +7510,7 @@
         <v>118</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -7599,7 +7599,7 @@
         <v>118</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -7688,7 +7688,7 @@
         <v>118</v>
       </c>
       <c r="AD78">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE78">
         <v>8000</v>
@@ -7777,7 +7777,7 @@
         <v>118</v>
       </c>
       <c r="AD79">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE79">
         <v>8000</v>
@@ -8133,7 +8133,7 @@
         <v>118</v>
       </c>
       <c r="AD83">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE83">
         <v>8000</v>
@@ -8222,7 +8222,7 @@
         <v>118</v>
       </c>
       <c r="AD84">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE84">
         <v>8000</v>
@@ -8311,7 +8311,7 @@
         <v>118</v>
       </c>
       <c r="AD85">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE85">
         <v>8000</v>
@@ -8400,7 +8400,7 @@
         <v>118</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE86">
         <v>8000</v>
@@ -8489,7 +8489,7 @@
         <v>118</v>
       </c>
       <c r="AD87">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE87">
         <v>8000</v>
@@ -8578,7 +8578,7 @@
         <v>118</v>
       </c>
       <c r="AD88">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AE88">
         <v>8000</v>
@@ -8934,7 +8934,7 @@
         <v>118</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9023,7 +9023,7 @@
         <v>118</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9112,7 +9112,7 @@
         <v>118</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9201,7 +9201,7 @@
         <v>118</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9290,7 +9290,7 @@
         <v>118</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9379,7 +9379,7 @@
         <v>118</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -9468,7 +9468,7 @@
         <v>118</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -9557,7 +9557,7 @@
         <v>118</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -9646,7 +9646,7 @@
         <v>118</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -9735,7 +9735,7 @@
         <v>118</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -9824,7 +9824,7 @@
         <v>118</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -9913,7 +9913,7 @@
         <v>118</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10002,7 +10002,7 @@
         <v>118</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10091,7 +10091,7 @@
         <v>118</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -10180,7 +10180,7 @@
         <v>118</v>
       </c>
       <c r="AD106">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE106">
         <v>8000</v>
@@ -10269,7 +10269,7 @@
         <v>118</v>
       </c>
       <c r="AD107">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE107">
         <v>8000</v>
@@ -10358,7 +10358,7 @@
         <v>118</v>
       </c>
       <c r="AD108">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE108">
         <v>8000</v>
@@ -10447,7 +10447,7 @@
         <v>118</v>
       </c>
       <c r="AD109">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE109">
         <v>8000</v>
@@ -10803,7 +10803,7 @@
         <v>118</v>
       </c>
       <c r="AD113">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="AE113">
         <v>8000</v>
@@ -10892,7 +10892,7 @@
         <v>118</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="AE114">
         <v>8000</v>
@@ -10981,7 +10981,7 @@
         <v>118</v>
       </c>
       <c r="AD115">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="AE115">
         <v>8000</v>
@@ -13206,7 +13206,7 @@
         <v>118</v>
       </c>
       <c r="AD140">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE140">
         <v>8000</v>
@@ -13295,7 +13295,7 @@
         <v>118</v>
       </c>
       <c r="AD141">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE141">
         <v>8000</v>
@@ -13384,7 +13384,7 @@
         <v>118</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -13740,7 +13740,7 @@
         <v>118</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -13829,7 +13829,7 @@
         <v>118</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -13918,7 +13918,7 @@
         <v>118</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -14013,7 +14013,7 @@
         <v>118</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -14102,7 +14102,7 @@
         <v>118</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -14191,7 +14191,7 @@
         <v>118</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -14280,7 +14280,7 @@
         <v>118</v>
       </c>
       <c r="AD152">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE152">
         <v>8000</v>
@@ -14375,7 +14375,7 @@
         <v>118</v>
       </c>
       <c r="AD153">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE153">
         <v>8000</v>
@@ -14470,7 +14470,7 @@
         <v>118</v>
       </c>
       <c r="AD154">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AE154">
         <v>8000</v>
